--- a/export/execution_report/execution_plan.xlsx
+++ b/export/execution_report/execution_plan.xlsx
@@ -425,463 +425,308 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Execution Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Best Date</t>
+          <t>Ticker</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Session</t>
+          <t>Volume (Shares)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Price (VND)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Value (VND)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Open-to-Close %</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Note</t>
+          <t>Strategic Rationale &amp; Slippage Control</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>April 20, 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ATO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FPT</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>4000</v>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ATO 09:00-09:15 (open higher than close)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>76900</v>
-      </c>
-      <c r="G2" t="n">
-        <v>307600000</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-0.60%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Peak in window, +0.0% vs 20/04.</t>
+          <t>SZC</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Full exit. Open-to-Close slippage minimized at -1.09%.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>April 20, 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ATO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SZC</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>6000</v>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ATO 09:00-09:15 (open higher than close)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>29000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>174000000</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.09%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Peak in window, +0.0% vs 20/04.</t>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Full exit. Open-to-Close slippage minimized at -0.91%.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>April 23, 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DGC</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3000</v>
+          <t>ATC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ATO 09:00-09:15 (open higher than close)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>55800</v>
-      </c>
-      <c r="G4" t="n">
-        <v>167400000</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.64%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Peak in window, +5.1% vs 20/04.</t>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Initial satellite deployment. Executed on technical support. Slippage at -0.20%.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>May 06, 2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ATO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>FTS</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>5000</v>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ATO 09:00-09:15 (open higher than close)</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>27500</v>
-      </c>
-      <c r="G5" t="n">
-        <v>137500000</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.92%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Peak in window, +0.0% vs 20/04.</t>
+          <t>DGC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Full exit. Executed into structural strength (-0.64% slippage).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>May 07, 2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ATO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>VPB</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>5000</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ATO 09:00-09:15 (open higher than close)</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>28150</v>
-      </c>
-      <c r="G6" t="n">
-        <v>140750000</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.14%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Peak in window, +0.4% vs 20/04.</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Full exit. Open-to-Close slippage minimized at -0.13%.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>May 07, 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ATC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2700</v>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ATC 14:30-14:45 (close lower than open)</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>58200</v>
-      </c>
-      <c r="G7" t="n">
-        <v>157140000</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Lowest in window (-5.1% vs 20/04).</t>
+          <t>VHC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Satellite deployment into defensive export sector. Slippage at -0.28%.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>May 11, 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ATC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>VTP</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>2500</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ATC 14:30-14:45 (close lower than open)</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>63200</v>
-      </c>
-      <c r="G8" t="n">
-        <v>158000000</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.96%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Lowest in window (-10.7% vs 20/04).</t>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Satellite deployment capturing logistics growth factor. Slippage at -0.96%.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>May 11, 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ATC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>CTR</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>1900</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ATC 14:30-14:45 (close lower than open)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>82300</v>
-      </c>
-      <c r="G9" t="n">
-        <v>156370000</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.53%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Lowest in window (-5.5% vs 20/04).</t>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Satellite deployment capturing telecom infrastructure factor. Slippage at -0.53%.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>May 11, 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VHC</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1800</v>
+          <t>ATC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY MORE</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ATC 14:30-14:45 (close lower than open)</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>60500</v>
-      </c>
-      <c r="G10" t="n">
-        <v>108900000</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.28%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Lowest in window (-3.5% vs 20/04).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BUY MORE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
           <t>FPT</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="E10" t="n">
         <v>500</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ATC 14:30-14:45 (close lower than open)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>70000</v>
-      </c>
-      <c r="G11" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.60%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Holding 4,000 → 4,500 shares (35.1%). Delta: +500.</t>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Final top-up to lock the defensive anchor weight at 35.11%. Slippage at -0.60%.</t>
         </is>
       </c>
     </row>

--- a/export/execution_report/execution_plan.xlsx
+++ b/export/execution_report/execution_plan.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Execution Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Volume (Shares)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Strategic Rationale &amp; Slippage Control</t>
         </is>
@@ -486,7 +474,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Full exit. Open-to-Close slippage minimized at -1.09%.</t>
+          <t>Full exit. Open-to-Close slippage minimized at -0.89%.</t>
         </is>
       </c>
     </row>
@@ -516,104 +504,104 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Full exit. Open-to-Close slippage minimized at -0.91%.</t>
+          <t>Full exit. Open-to-Close slippage minimized at -0.47%.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>April 23, 2026</t>
+          <t>May 06, 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ATC</t>
+          <t>ATO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SIP</t>
+          <t>DGC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Initial satellite deployment. Executed on technical support. Slippage at -0.20%.</t>
+          <t>Full exit. Executed into structural strength (-0.53% slippage).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>May 06, 2026</t>
+          <t>May 11, 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ATO</t>
+          <t>ATC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DGC</t>
+          <t>VTP</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Full exit. Executed into structural strength (-0.64% slippage).</t>
+          <t>Satellite deployment capturing logistics growth factor. Slippage at -0.61%.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>May 07, 2026</t>
+          <t>May 11, 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ATO</t>
+          <t>ATC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VPB</t>
+          <t>CTR</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5000</v>
+        <v>1900</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Full exit. Open-to-Close slippage minimized at -0.13%.</t>
+          <t>Satellite deployment capturing telecom infrastructure factor. Slippage at -0.36%.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>May 07, 2026</t>
+          <t>May 11, 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -623,57 +611,57 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>BUY MORE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VHC</t>
+          <t>FPT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Satellite deployment into defensive export sector. Slippage at -0.28%.</t>
+          <t>Final top-up to lock the defensive anchor weight at 35.11%. Slippage at -0.07%.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>May 11, 2026</t>
+          <t>May 14, 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATC</t>
+          <t>ATO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VTP</t>
+          <t>VPB</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Satellite deployment capturing logistics growth factor. Slippage at -0.96%.</t>
+          <t>Full exit. Open-to-Close slippage minimized at -0.17%.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>May 11, 2026</t>
+          <t>June 02, 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -688,22 +676,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CTR</t>
+          <t>SIP</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1900</v>
+        <v>3100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Satellite deployment capturing telecom infrastructure factor. Slippage at -0.53%.</t>
+          <t>Initial satellite deployment. Executed on technical support. Slippage at -0.43%.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>May 11, 2026</t>
+          <t>June 05, 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -713,20 +701,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BUY MORE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FPT</t>
+          <t>VHC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>500</v>
+        <v>1900</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Final top-up to lock the defensive anchor weight at 35.11%. Slippage at -0.60%.</t>
+          <t>Satellite deployment into defensive export sector. Slippage at -0.44%.</t>
         </is>
       </c>
     </row>
